--- a/02_DIA_inicio_2026_analisis_assets/rbd_9422_escuela-centro-educ-rep-mexicana_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9422_escuela-centro-educ-rep-mexicana_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8F5F87E-EEB9-41B5-B0A5-F76F91C49B04}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F3DDD07-C727-4EF1-804C-29250D8D3A31}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02D67EF3-A277-4FE5-9F70-076C9C5EC5E9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB549391-C0C5-4255-A14A-D7877751E7BF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11D571AA-8C3F-4C56-9D63-6C59B6151518}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DBEDBD5-242A-4798-8D20-A895423F1710}"/>
 </file>